--- a/withpom/src/test/resources/loginData.xlsx
+++ b/withpom/src/test/resources/loginData.xlsx
@@ -126,7 +126,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -268,7 +268,7 @@
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="1" t="s">
         <v>1</v>
       </c>
     </row>
